--- a/docs/工作簿1_蛞蝓猫同步.xlsx
+++ b/docs/工作簿1_蛞蝓猫同步.xlsx
@@ -570,7 +570,7 @@
     <row r="3">
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>业力上限5初始3</t>
+          <t>业力上限10初始3；饱食上限6</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="C4" s="0" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="C5" s="0" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="C6" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="C7" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="C9" s="0" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="C10" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="C11" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="C12" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="C13" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="C14" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="C15" s="0" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="C16" s="0" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="C17" s="0" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
-          <t>1血。1费转移到别人的手牌。加入一张秃鹫。</t>
+          <t>1血。1费转移到别人的手牌。转移后回合结束召唤一只秃鹫（加入生物手牌，每次转移仅一次）。</t>
         </is>
       </c>
       <c r="G22" s="0" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
-          <t>拾荒者+5，射线虫+3，秃鹫+1；泡水果+5，炸药+1，炸矛+1，电矛+1</t>
+          <t>拾荒者+3，射线虫+2，秃鹫+1；泡水果+3，炸药+1，炸矛+1，电矛+1，石子+1，钢筋+1</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
-          <t>拾荒者+5；有色珍珠+1，闪光果+10，炸矛+3，炸药+3；业力上限++</t>
+          <t>拾荒者+3；有色珍珠+1，闪光果+5，炸矛+2，炸药+2；业力上限++</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
-          <t>金蜥蜴+5，秃鹫+3，管虫+3；业力上限++</t>
+          <t>金蜥蜴+3，秃鹫+2，管虫+2；钢筋+2，石子+2，炸矛+1，电矛+1，泡水果+2；业力上限++</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
-          <t>小面条+3，金蜥蜴+5，秃鹫+1；有色珍珠+1，炸矛+3；业力上限++</t>
+          <t>小面条+2，金蜥蜴+3，秃鹫+1；有色珍珠+1，炸矛+2，钢筋+2，石子+2，爆米花+1；业力上限++</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
-          <t>烈焰蜈蚣+1，烈焰蜥蜴+2；业力上限++</t>
+          <t>烈焰蜈蚣+1，烈焰蜥蜴+1；钢筋+2，石子+2，炸药+1，炸矛+1，烟雾果+1，泡水果+1；业力上限++</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t>泡水果+10，有色珍珠+1</t>
+          <t>泡水果+5，有色珍珠+1，石子+1，钢筋+1</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
-          <t>拾荒者+3，小面条+3；烟雾果+10，炸矛+3，电矛+3；业力上限++</t>
+          <t>拾荒者+2，小面条+2；烟雾果+4，爆米花+1，炸矛+2，电矛+2；业力上限++</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="E39" s="0" t="inlineStr">
         <is>
-          <t>小面条+3，拾荒者+5，烈焰蜈蚣+1；烟雾果+5，闪光果+5，炸药+5，炸矛+3，电矛+3，有色珍珠+2</t>
+          <t>小面条+2，拾荒者+3，烈焰蜈蚣+1；烟雾果+3，闪光果+3，炸药+3，炸矛+2，电矛+2，有色珍珠+1</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="E40" s="0" t="inlineStr">
         <is>
-          <t>钢秃鹫+5；质量稀释电池+1，有色珍珠+1；业力上限++</t>
+          <t>钢秃鹫+3；质量稀释电池+1，有色珍珠+1，钢筋+2，石子+2，炸矛+1，泡水果+1；业力上限++</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       <c r="C41" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="0" t="n">
         <v>4</v>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -1411,7 +1411,7 @@
       <c r="C42" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="0" t="n">
         <v>4</v>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -1434,7 +1434,7 @@
       <c r="C43" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="0" t="n">
         <v>4</v>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -1457,7 +1457,7 @@
       <c r="C44" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="0" t="n">
         <v>4</v>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -1480,7 +1480,7 @@
       <c r="C45" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="0" t="n">
         <v>4</v>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -1526,11 +1526,11 @@
         </is>
       </c>
       <c r="C47" s="0" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E47" s="0" t="inlineStr">
         <is>
-          <t>耗能0：在手牌中时每回合获得2点固定饱食度</t>
+          <t>耗能0：在手牌中时每回合获得1点固定饱食度</t>
         </is>
       </c>
       <c r="G47" s="0" t="inlineStr">
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="C49" s="0" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E49" s="0" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="C51" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E51" s="0" t="inlineStr">
         <is>
@@ -1689,6 +1689,26 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="0" t="inlineStr">
+        <is>
+          <t>爆米花</t>
+        </is>
+      </c>
+      <c r="B54" s="0" t="inlineStr">
+        <is>
+          <t>物品</t>
+        </is>
+      </c>
+      <c r="C54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="0" t="inlineStr">
+        <is>
+          <t>耗能3：立即获得全部饱食。</t>
+        </is>
+      </c>
+    </row>
     <row r="56">
       <c r="A56" s="0" t="inlineStr">
         <is>
@@ -1719,7 +1739,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>生物不占手牌卡槽（只有管虫拿在手里占手牌）！！！！！在手牌中时回合结束才出伤！！！对标的是杀戮尖塔里面的诅咒，除了可以被攻击牌选中不会更复杂的打牌逻辑改变了，只是除了打出(躲避)也可以被杀死而且还有好处。暂定就是动态的血量加自身的特性，通过牌所在位置来增加变化，体现生物的运动和索敌。生物的伤害都是回合结束结算，提供丰富的反制空间。为什么要设计大量耗费拉扯的牌呢，因为蛞蝓猫的攻击收益是对面防越少越高，逼迫对面耗费无法起防和占手牌也是重要收益。加入方式会写在技能牌里。</t>
+          <t>生物不占手牌卡槽（只有管虫拿在手里占手牌）！！！！！在手牌中时回合结束才出伤！！！对标的是杀戮尖塔里面的诅咒，除了可以被攻击牌选中不会更复杂的打牌逻辑改变了，只是除了打出(躲避)也可以被杀死而且还有好处。暂定就是动态的血量加自身的特性，通过牌所在位置来增加变化，体现生物的运动和索敌。生物的伤害都是回合结束结算，提供丰富的反制空间。为什么要设计大量耗费拉扯的牌呢，因为蛞蝓猫的攻击收益是对面防越少越高，逼迫对面耗费无法起防和占手牌也是重要收益。加入方式会写在技能牌里。打出（躲避）的生物未被杀死，回到可召唤池。</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1756,7 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>统一耗能为2。相邻关系（双向）：郊区-城堡，郊区-绝壁-群岛-农场-地窟-外层，郊区-迷宫-地窟-外层；郊区-迷宫-地窟-巨构。打出见闻牌会在见闻牌堆中加入一张数量较少的相邻牌（优先解锁新的地方）；业力上限只有第一次打+1</t>
+          <t>统一耗能为2。相邻关系（双向）：郊区-城堡，郊区-绝壁-群岛-农场-地窟-外层，郊区-迷宫-地窟-外层；郊区-迷宫-地窟-巨构。打出见闻牌会在见闻牌堆中加入一张数量较少的相邻牌（优先解锁新的地方）；业力上限第一次打+2、之后各+1</t>
         </is>
       </c>
     </row>

--- a/docs/工作簿1_蛞蝓猫同步.xlsx
+++ b/docs/工作簿1_蛞蝓猫同步.xlsx
@@ -700,7 +700,7 @@
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
-          <t>耗能2：3伤，转换当前的动能。【插入】时占入对方手牌，每回合-2力直到耗1能打出</t>
+          <t>耗能2：3伤，转换当前的动能。【插入】时占入对方手牌，持有者所有攻击（含生物攻击）数值-2/根直到耗1能打出</t>
         </is>
       </c>
       <c r="G8" s="0" t="inlineStr">
